--- a/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,13 +706,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45163.60949987368</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45253</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -755,19 +751,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25">
       <c r="E25" s="7" t="n"/>
     </row>
@@ -803,7 +786,7 @@
       </c>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="6" t="n">
-        <v>4967.5</v>
+        <v>5215.875</v>
       </c>
       <c r="E27" s="7" t="n"/>
     </row>
@@ -820,7 +803,7 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="6" t="n">
-        <v>6210</v>
+        <v>6520.5</v>
       </c>
       <c r="E28" s="7" t="n"/>
     </row>
@@ -837,7 +820,7 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="6" t="n">
-        <v>5322.5</v>
+        <v>5588.625</v>
       </c>
       <c r="E29" s="7" t="n"/>
     </row>
@@ -854,7 +837,7 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="6" t="n">
-        <v>6742.5</v>
+        <v>7079.625</v>
       </c>
       <c r="E30" s="7" t="n"/>
     </row>
@@ -871,7 +854,7 @@
       </c>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="6" t="n">
-        <v>5677.5</v>
+        <v>5961.375</v>
       </c>
       <c r="E31" s="7" t="n"/>
     </row>
@@ -888,7 +871,7 @@
       </c>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="6" t="n">
-        <v>7273.75</v>
+        <v>7637.438</v>
       </c>
       <c r="E32" s="7" t="n"/>
     </row>
@@ -905,7 +888,7 @@
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>6210</v>
+        <v>6520.5</v>
       </c>
       <c r="E33" s="7" t="n"/>
     </row>
@@ -922,7 +905,7 @@
       </c>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="6" t="n">
-        <v>8342.5</v>
+        <v>8759.625</v>
       </c>
       <c r="E34" s="7" t="n"/>
     </row>
@@ -930,8 +913,6 @@
       <c r="A35" s="4" t="n"/>
       <c r="E35" s="7" t="n"/>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -942,18 +923,18 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,7 +706,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,7 +706,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,7 +706,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,7 +706,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
+++ b/LISTAS/ma/TENDEDERO EXTENSIBLE LISDISMAY.xlsx
@@ -706,9 +706,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45264.64767383689</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="13">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -751,6 +755,19 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="E25" s="7" t="n"/>
     </row>
@@ -786,7 +803,7 @@
       </c>
       <c r="C27" s="11" t="n"/>
       <c r="D27" s="6" t="n">
-        <v>5215.875</v>
+        <v>8097.64</v>
       </c>
       <c r="E27" s="7" t="n"/>
     </row>
@@ -803,7 +820,7 @@
       </c>
       <c r="C28" s="11" t="n"/>
       <c r="D28" s="6" t="n">
-        <v>6520.5</v>
+        <v>10123.07</v>
       </c>
       <c r="E28" s="7" t="n"/>
     </row>
@@ -820,7 +837,7 @@
       </c>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="6" t="n">
-        <v>5588.625</v>
+        <v>8676.34</v>
       </c>
       <c r="E29" s="7" t="n"/>
     </row>
@@ -837,7 +854,7 @@
       </c>
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="6" t="n">
-        <v>7079.625</v>
+        <v>10991.11</v>
       </c>
       <c r="E30" s="7" t="n"/>
     </row>
@@ -854,7 +871,7 @@
       </c>
       <c r="C31" s="11" t="n"/>
       <c r="D31" s="6" t="n">
-        <v>5961.375</v>
+        <v>9255.030000000001</v>
       </c>
       <c r="E31" s="7" t="n"/>
     </row>
@@ -871,7 +888,7 @@
       </c>
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="6" t="n">
-        <v>7637.438</v>
+        <v>11857.12</v>
       </c>
       <c r="E32" s="7" t="n"/>
     </row>
@@ -888,7 +905,7 @@
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>6520.5</v>
+        <v>10123.07</v>
       </c>
       <c r="E33" s="7" t="n"/>
     </row>
@@ -905,7 +922,7 @@
       </c>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="6" t="n">
-        <v>8759.625</v>
+        <v>13599.31</v>
       </c>
       <c r="E34" s="7" t="n"/>
     </row>
@@ -913,6 +930,8 @@
       <c r="A35" s="4" t="n"/>
       <c r="E35" s="7" t="n"/>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -923,18 +942,18 @@
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
